--- a/data/trans_dic/P5B_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P5B_R-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con calidad medioambiental mala o muy mala en la zona de residencia</t>
+          <t>Hogares con calidad medioambiental mala o muy mala en la zona de residencia (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -653,7 +654,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -673,7 +674,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -683,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -693,7 +694,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 8,91</t>
+          <t>0,97; 8,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 10,12</t>
+          <t>1,17; 10,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,94</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,21</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,65</t>
+          <t>0,0; 5,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,73</t>
+          <t>0,0; 5,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,79</t>
+          <t>0,0; 4,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,66</t>
+          <t>1,2; 5,78</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 6,56</t>
+          <t>1,33; 6,62</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,07</t>
+          <t>0,0; 2,04</t>
         </is>
       </c>
     </row>
@@ -813,7 +814,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -833,7 +834,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 7,91</t>
+          <t>0,92; 8,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,3</t>
+          <t>0,0; 7,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,79</t>
+          <t>0,0; 3,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,95</t>
+          <t>0,0; 3,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 8,87</t>
+          <t>0,93; 8,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,55</t>
+          <t>0,0; 6,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,75</t>
+          <t>0,0; 3,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 7,47</t>
+          <t>0,61; 7,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,28; 6,7</t>
+          <t>1,42; 6,69</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,42</t>
+          <t>0,59; 5,13</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,87</t>
+          <t>0,0; 2,8</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,04</t>
+          <t>0,48; 4,33</t>
         </is>
       </c>
     </row>
@@ -996,7 +997,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1006,52 +1007,52 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,34</t>
+          <t>0,0; 2,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,92</t>
+          <t>0,0; 4,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,12</t>
+          <t>0,0; 8,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,12</t>
+          <t>0,0; 2,13</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,68</t>
+          <t>0,0; 3,24</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,07</t>
+          <t>0,0; 4,28</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1079,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1118,7 +1119,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,83; 8,76</t>
+          <t>2,73; 8,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,55</t>
+          <t>0,36; 3,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,57</t>
+          <t>0,85; 4,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,3</t>
+          <t>0,0; 39,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 5,26</t>
+          <t>0,91; 5,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,24</t>
+          <t>0,42; 4,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 4,95</t>
+          <t>1,01; 5,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,48</t>
+          <t>0,0; 2,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,32; 5,95</t>
+          <t>2,47; 6,14</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,29</t>
+          <t>0,63; 3,03</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,91</t>
+          <t>1,23; 3,9</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 28,94</t>
+          <t>0,35; 28,08</t>
         </is>
       </c>
     </row>
@@ -1276,47 +1277,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,02; 12,62</t>
+          <t>2,15; 12,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,73</t>
+          <t>0,0; 4,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,22; 6,95</t>
+          <t>1,24; 6,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,47</t>
+          <t>0,54; 5,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,51; 9,14</t>
+          <t>2,11; 9,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,15</t>
+          <t>0,0; 4,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,69</t>
+          <t>0,0; 3,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,03; 9,06</t>
+          <t>2,92; 8,88</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1326,12 +1327,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,65</t>
+          <t>0,98; 4,5</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,22</t>
+          <t>0,65; 3,31</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1354,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1393,7 +1394,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1416,37 +1417,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,89; 8,45</t>
+          <t>0,88; 7,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,14; 9,89</t>
+          <t>1,15; 9,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,93; 7,37</t>
+          <t>0,92; 8,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,84; 10,81</t>
+          <t>1,86; 10,86</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,88; 8,54</t>
+          <t>0,89; 8,11</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1456,22 +1457,22 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,17; 6,87</t>
+          <t>2,0; 7,5</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,55; 7,07</t>
+          <t>1,53; 6,94</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,92</t>
+          <t>0,44; 3,8</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,83</t>
+          <t>0,0; 2,37</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1494,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1503,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1513,12 +1514,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1533,7 +1534,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,59; 5,38</t>
+          <t>2,62; 5,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,13</t>
+          <t>1,13; 3,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,06; 2,83</t>
+          <t>1,07; 2,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,44; 17,95</t>
+          <t>0,48; 20,66</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,41</t>
+          <t>1,91; 4,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,59</t>
+          <t>0,8; 2,73</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,14</t>
+          <t>0,51; 1,9</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,21</t>
+          <t>0,76; 2,23</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,63; 4,52</t>
+          <t>2,58; 4,45</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,52</t>
+          <t>1,22; 2,6</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,11</t>
+          <t>0,91; 2,09</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,86; 9,83</t>
+          <t>0,82; 10,33</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con calidad medioambiental mala o muy mala en la zona de residencia (tasa de respuesta: 99,82%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2815</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2665</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1296</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1487</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>4115</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>3962</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1487</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>777; 6953</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>712; 6401</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3987</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4002</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5513</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1820; 8791</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1774; 8832</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4880</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2043</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1608</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2388</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>763</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2502</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>4431</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2508</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1377</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>3169</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>631; 5511</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4900</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3093</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3426</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>629; 5532</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4518</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3390</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>584; 7073</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1932; 9106</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>789; 6831</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4902</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>908; 8241</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>768</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1425</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>1448</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>1425</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4077</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2438</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3160</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5507</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3027</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4354</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4952</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>7957</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1915</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3632</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>27398</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>3918</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2879</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>4130</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1580</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>11874</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>4794</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>7762</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>28978</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>4130; 13404</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>496; 5342</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1398; 7600</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 85836</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1348; 7922</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>679; 7392</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1718; 9401</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5960</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>7400; 18410</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>1882; 9033</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>4114; 13065</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>1512; 122745</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>4375</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>3310</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2677</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>3834</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1406</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1650</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>8209</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>4716</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>4326</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>1487; 8501</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3894</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1257; 7046</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>646; 6796</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1786; 7800</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4399</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5409</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>4491; 13649</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3503</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>1957; 9030</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>1819; 9349</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2085</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1985</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>3882</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>2593</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1098</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>5967</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>4579</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>1098</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>660; 5532</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>613; 4999</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>556; 4902</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1347; 7859</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>658; 6006</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3906</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>2938; 11039</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>1943; 8833</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>565; 4873</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3341</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>19275</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>9636</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>9356</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>30742</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>15919</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>8349</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>6299</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>9741</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>35195</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>17986</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>15655</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>40484</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>13163; 27622</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>5359; 15093</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>5598; 15463</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>3151; 135814</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>10112; 22704</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>4302; 14603</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>2910; 10846</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>5645; 16693</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>26632; 45898</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>12294; 26308</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>9972; 22826</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>11467; 145152</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/P5B_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P5B_R-Clase-trans_dic.xlsx
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 8,64</t>
+          <t>0,98; 8,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,17; 10,54</t>
+          <t>1,18; 10,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,57</t>
+          <t>0,0; 5,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,51</t>
+          <t>0,0; 6,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -752,17 +752,17 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,08</t>
+          <t>0,0; 4,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 5,78</t>
+          <t>0,97; 5,45</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,33; 6,62</t>
+          <t>1,01; 5,58</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,04</t>
+          <t>0,0; 2,2</t>
         </is>
       </c>
     </row>
@@ -857,27 +857,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 8,02</t>
+          <t>0,91; 7,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,5</t>
+          <t>0,0; 7,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,76</t>
+          <t>0,0; 4,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,62</t>
+          <t>0,0; 3,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 8,2</t>
+          <t>0,93; 8,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -887,32 +887,32 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,64</t>
+          <t>0,0; 4,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 7,4</t>
+          <t>0,62; 7,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,42; 6,69</t>
+          <t>1,38; 6,25</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,13</t>
+          <t>0,59; 5,04</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,8</t>
+          <t>0,0; 2,59</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,33</t>
+          <t>0,48; 4,0</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,13</t>
+          <t>0,0; 6,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1017,12 +1017,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,9</t>
+          <t>0,0; 3,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,65</t>
+          <t>0,0; 5,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,17 +1032,17 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,62</t>
+          <t>0,0; 7,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,13</t>
+          <t>0,0; 2,1</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,24</t>
+          <t>0,0; 3,77</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,28</t>
+          <t>0,0; 4,45</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,73; 8,86</t>
+          <t>2,89; 9,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,91</t>
+          <t>0,37; 3,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 4,64</t>
+          <t>0,88; 4,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,23</t>
+          <t>0,0; 42,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,91; 5,33</t>
+          <t>0,89; 5,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,58</t>
+          <t>0,42; 4,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,01; 5,5</t>
+          <t>1,07; 4,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,73</t>
+          <t>0,0; 2,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,47; 6,14</t>
+          <t>2,38; 6,18</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,03</t>
+          <t>0,69; 3,21</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,9</t>
+          <t>1,24; 3,95</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 28,08</t>
+          <t>0,34; 25,69</t>
         </is>
       </c>
     </row>
@@ -1277,27 +1277,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,15; 12,3</t>
+          <t>2,98; 12,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,17</t>
+          <t>0,0; 3,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,24; 6,94</t>
+          <t>1,23; 6,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,69</t>
+          <t>0,54; 5,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,11; 9,23</t>
+          <t>1,58; 9,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,44</t>
+          <t>0,0; 4,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,33</t>
+          <t>0,0; 3,5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,92; 8,88</t>
+          <t>2,92; 9,0</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,89</t>
+          <t>0,0; 2,13</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,5</t>
+          <t>1,0; 4,95</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,31</t>
+          <t>0,54; 3,25</t>
         </is>
       </c>
     </row>
@@ -1417,17 +1417,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,88; 7,39</t>
+          <t>0,88; 7,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,15; 9,4</t>
+          <t>1,14; 9,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,92; 8,12</t>
+          <t>0,93; 8,06</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,86; 10,86</t>
+          <t>1,82; 10,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,89; 8,11</t>
+          <t>0,89; 8,49</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1452,27 +1452,27 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,42</t>
+          <t>0,0; 4,69</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,0; 7,5</t>
+          <t>1,86; 7,54</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,53; 6,94</t>
+          <t>1,54; 6,81</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,8</t>
+          <t>0,44; 3,87</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,37</t>
+          <t>0,0; 2,68</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,62; 5,5</t>
+          <t>2,6; 5,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,17</t>
+          <t>1,09; 3,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,07; 2,96</t>
+          <t>1,03; 2,84</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 20,66</t>
+          <t>0,41; 18,36</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,3</t>
+          <t>2,0; 4,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,73</t>
+          <t>0,77; 2,68</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,9</t>
+          <t>0,53; 1,95</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,23</t>
+          <t>0,69; 2,29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,58; 4,45</t>
+          <t>2,56; 4,41</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,6</t>
+          <t>1,17; 2,56</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,09</t>
+          <t>0,93; 2,05</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,82; 10,33</t>
+          <t>0,84; 12,21</t>
         </is>
       </c>
     </row>
@@ -1927,12 +1927,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>777; 6953</t>
+          <t>788; 7138</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>712; 6401</t>
+          <t>717; 6160</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1947,12 +1947,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3987</t>
+          <t>0; 4268</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4002</t>
+          <t>0; 4943</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1962,17 +1962,17 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 5513</t>
+          <t>0; 5647</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1820; 8791</t>
+          <t>1470; 8293</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1774; 8832</t>
+          <t>1353; 7441</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 4880</t>
+          <t>0; 5260</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>631; 5511</t>
+          <t>626; 5440</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4900</t>
+          <t>0; 4831</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3093</t>
+          <t>0; 3633</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3426</t>
+          <t>0; 3417</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>629; 5532</t>
+          <t>629; 5852</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4518</t>
+          <t>0; 4514</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3390</t>
+          <t>0; 4147</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>584; 7073</t>
+          <t>594; 7396</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1932; 9106</t>
+          <t>1874; 8505</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>789; 6831</t>
+          <t>781; 6719</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 4902</t>
+          <t>0; 4546</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>908; 8241</t>
+          <t>918; 7612</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4077</t>
+          <t>0; 4506</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2363,12 +2363,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2438</t>
+          <t>0; 2631</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3160</t>
+          <t>0; 3440</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2378,17 +2378,17 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 5507</t>
+          <t>0; 4918</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3027</t>
+          <t>0; 2988</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 4354</t>
+          <t>0; 5074</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 4952</t>
+          <t>0; 5144</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4130; 13404</t>
+          <t>4374; 13728</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>496; 5342</t>
+          <t>504; 5146</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1398; 7600</t>
+          <t>1439; 7807</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 85836</t>
+          <t>0; 92080</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1348; 7922</t>
+          <t>1329; 7942</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>679; 7392</t>
+          <t>680; 7319</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1718; 9401</t>
+          <t>1826; 8480</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 5960</t>
+          <t>0; 5464</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7400; 18410</t>
+          <t>7128; 18521</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1882; 9033</t>
+          <t>2059; 9551</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4114; 13065</t>
+          <t>4148; 13218</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1512; 122745</t>
+          <t>1497; 112297</t>
         </is>
       </c>
     </row>
@@ -2759,27 +2759,27 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1487; 8501</t>
+          <t>2057; 8790</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3894</t>
+          <t>0; 3477</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1257; 7046</t>
+          <t>1248; 7060</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>646; 6796</t>
+          <t>643; 6768</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1786; 7800</t>
+          <t>1337; 7987</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2789,32 +2789,32 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4399</t>
+          <t>0; 4603</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 5409</t>
+          <t>0; 5694</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4491; 13649</t>
+          <t>4492; 13824</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 3503</t>
+          <t>0; 3947</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1957; 9030</t>
+          <t>2015; 9935</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1819; 9349</t>
+          <t>1533; 9165</t>
         </is>
       </c>
     </row>
@@ -2967,17 +2967,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>660; 5532</t>
+          <t>662; 5620</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>613; 4999</t>
+          <t>604; 4873</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>556; 4902</t>
+          <t>559; 4862</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1347; 7859</t>
+          <t>1315; 7750</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>658; 6006</t>
+          <t>662; 6284</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -3002,27 +3002,27 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3906</t>
+          <t>0; 3377</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2938; 11039</t>
+          <t>2734; 11100</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1943; 8833</t>
+          <t>1954; 8664</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>565; 4873</t>
+          <t>565; 4956</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 3341</t>
+          <t>0; 3777</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>13163; 27622</t>
+          <t>13083; 27980</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5359; 15093</t>
+          <t>5181; 16126</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5598; 15463</t>
+          <t>5374; 14832</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3151; 135814</t>
+          <t>2726; 120684</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>10112; 22704</t>
+          <t>10573; 23863</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4302; 14603</t>
+          <t>4120; 14360</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2910; 10846</t>
+          <t>3006; 11106</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>5645; 16693</t>
+          <t>5172; 17084</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>26632; 45898</t>
+          <t>26373; 45436</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12294; 26308</t>
+          <t>11791; 25853</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9972; 22826</t>
+          <t>10130; 22399</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>11467; 145152</t>
+          <t>11809; 171521</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P5B_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P5B_R-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,62 +649,62 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>3,5%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>4,39%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2,71%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2,97%</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2,71%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 8,87</t>
+          <t>0,0; 5,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 10,14</t>
+          <t>0,0; 6,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -732,37 +732,37 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 4,8</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,98; 8,91</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1,18; 9,92</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,96</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 6,8</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,17</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 5,45</t>
+          <t>0,94; 5,66</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 5,58</t>
+          <t>1,32; 6,36</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,2</t>
+          <t>0,0; 2,6</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3,54%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2,69%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>2,97%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2,46%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>0,74%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>3,54%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,33%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 7,92</t>
+          <t>0,92; 8,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,39</t>
+          <t>0,0; 6,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,41</t>
+          <t>0,0; 3,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,61</t>
+          <t>0,55; 7,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 8,67</t>
+          <t>0,9; 7,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,66</t>
+          <t>0,0; 9,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,46</t>
+          <t>0,0; 3,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 7,74</t>
+          <t>0,0; 4,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,38; 6,25</t>
+          <t>1,28; 6,7</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,04</t>
+          <t>0,59; 5,5</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,59</t>
+          <t>0,0; 2,87</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,0</t>
+          <t>0,5; 4,12</t>
         </is>
       </c>
     </row>
@@ -929,62 +929,62 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2,51%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1,15%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -997,52 +997,52 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 4,34</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 5,92</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 6,77</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 9,1</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 6,13</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,13</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,06</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,7</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,1</t>
+          <t>0,0; 2,12</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,77</t>
+          <t>0,0; 3,68</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,45</t>
+          <t>0,0; 5,3</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2,64%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>5,26%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1,4%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>2,22%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>12,52%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,64%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,89; 9,07</t>
+          <t>0,88; 5,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,77</t>
+          <t>0,42; 4,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 4,76</t>
+          <t>0,88; 4,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,08</t>
+          <t>0,0; 2,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,89; 5,35</t>
+          <t>2,83; 8,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,54</t>
+          <t>0,36; 3,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,07; 4,96</t>
+          <t>0,74; 4,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,5</t>
+          <t>0,0; 7,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,38; 6,18</t>
+          <t>2,32; 5,95</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,21</t>
+          <t>0,68; 3,29</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,95</t>
+          <t>1,25; 3,99</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 25,69</t>
+          <t>0,25; 4,73</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4,54%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>6,33%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>0,74%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>3,26%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>4,54%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,98; 12,72</t>
+          <t>1,51; 9,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,72</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,23; 6,95</t>
+          <t>0,0; 5,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,67</t>
+          <t>0,0; 3,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,58; 9,45</t>
+          <t>3,02; 12,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,64</t>
+          <t>1,22; 6,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,5</t>
+          <t>0,54; 5,63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,92; 9,0</t>
+          <t>3,03; 9,06</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,13</t>
+          <t>0,0; 1,89</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,95</t>
+          <t>1,0; 4,65</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,25</t>
+          <t>0,6; 3,36</t>
         </is>
       </c>
     </row>
@@ -1349,44 +1349,44 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5,36%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>2,78%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>3,73%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>2,98%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>5,36%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
           <t>4,05%</t>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,88; 7,51</t>
+          <t>1,84; 10,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,14; 9,16</t>
+          <t>0,88; 8,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,93; 8,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
+          <t>0,0; 5,07</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0,89; 8,45</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1,15; 10,7</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0,93; 7,37</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>1,82; 10,71</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0,89; 8,49</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,69</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,86; 7,54</t>
+          <t>2,17; 6,87</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,54; 6,81</t>
+          <t>1,54; 6,87</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,87</t>
+          <t>0,44; 3,92</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,68</t>
+          <t>0,0; 2,38</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>3,83%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>2,03%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>1,79%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4,68%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,6; 5,57</t>
+          <t>1,86; 4,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,39</t>
+          <t>0,77; 2,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,84</t>
+          <t>0,5; 2,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,41; 18,36</t>
+          <t>0,73; 2,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,51</t>
+          <t>2,59; 5,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,68</t>
+          <t>1,18; 3,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,95</t>
+          <t>1,06; 2,92</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,29</t>
+          <t>0,41; 2,91</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,56; 4,41</t>
+          <t>2,63; 4,52</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,56</t>
+          <t>1,13; 2,62</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,05</t>
+          <t>0,95; 2,07</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,84; 12,21</t>
+          <t>0,75; 2,03</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,62 +1859,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1296</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1429</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>2815</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>2665</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1300</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1296</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>4115</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>3962</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1487</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>4115</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>3962</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1487</t>
+          <t>1429</t>
         </is>
       </c>
     </row>
@@ -1927,12 +1927,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>788; 7138</t>
+          <t>0; 4049</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>717; 6160</t>
+          <t>0; 4541</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1942,37 +1942,37 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>0; 5811</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>786; 7172</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>716; 6024</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0; 4268</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0; 4943</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0; 5647</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1470; 8293</t>
+          <t>1436; 8612</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1353; 7441</t>
+          <t>1767; 8485</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 5260</t>
+          <t>0; 5800</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2388</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>763</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2456</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>2043</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1608</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>613</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2388</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>900</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>763</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2502</t>
+          <t>759</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3169</t>
+          <t>3215</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>626; 5440</t>
+          <t>619; 5988</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4831</t>
+          <t>0; 4503</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3633</t>
+          <t>0; 3488</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3417</t>
+          <t>499; 7294</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>629; 5852</t>
+          <t>621; 5432</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4514</t>
+          <t>0; 6079</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4147</t>
+          <t>0; 3122</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>594; 7396</t>
+          <t>0; 4286</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1874; 8505</t>
+          <t>1744; 9119</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>781; 6719</t>
+          <t>790; 7330</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 4546</t>
+          <t>0; 5025</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>918; 7612</t>
+          <t>944; 7735</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,62 +2275,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1429</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>768</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>1448</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1425</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>1448</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1425</t>
+          <t>1429</t>
         </is>
       </c>
     </row>
@@ -2343,52 +2343,52 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0; 3642</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4027</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0; 4506</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5179</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4080</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0; 2631</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3440</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0; 4918</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 2988</t>
+          <t>0; 3009</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 5074</t>
+          <t>0; 4946</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 5144</t>
+          <t>0; 5847</t>
         </is>
       </c>
     </row>
@@ -2415,32 +2415,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3918</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2879</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4130</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1472</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>7957</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1915</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>3632</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>27398</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>3918</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2879</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>4130</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1580</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>28978</t>
+          <t>4732</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4374; 13728</t>
+          <t>1312; 7816</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>504; 5146</t>
+          <t>672; 6836</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1439; 7807</t>
+          <t>1509; 8456</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 92080</t>
+          <t>0; 5808</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1329; 7942</t>
+          <t>4280; 13253</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>680; 7319</t>
+          <t>492; 4845</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1826; 8480</t>
+          <t>1217; 7302</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 5464</t>
+          <t>0; 14285</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7128; 18521</t>
+          <t>6965; 17849</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2059; 9551</t>
+          <t>2034; 9795</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4148; 13218</t>
+          <t>4175; 13357</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1497; 112297</t>
+          <t>971; 18050</t>
         </is>
       </c>
     </row>
@@ -2628,37 +2628,37 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>3834</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1406</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1567</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>4375</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>695</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>3310</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2677</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>3834</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>1406</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>2746</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4326</t>
+          <t>4313</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2057; 8790</t>
+          <t>1280; 7725</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3477</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1248; 7060</t>
+          <t>0; 5103</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>643; 6768</t>
+          <t>0; 5778</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1337; 7987</t>
+          <t>2088; 8720</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3487</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4603</t>
+          <t>1240; 7057</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 5694</t>
+          <t>645; 6680</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4492; 13824</t>
+          <t>4651; 13923</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 3947</t>
+          <t>0; 3509</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2015; 9935</t>
+          <t>2012; 9341</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1533; 9165</t>
+          <t>1590; 8966</t>
         </is>
       </c>
     </row>
@@ -2831,42 +2831,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,44 +2899,44 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>3882</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2593</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>2085</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>1985</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>1800</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>3882</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>2593</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>1098</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
           <t>5967</t>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1098</t>
+          <t>910</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>662; 5620</t>
+          <t>1335; 7822</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>604; 4873</t>
+          <t>653; 6324</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>559; 4862</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
+          <t>0; 3460</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>667; 6327</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>610; 5690</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>559; 4449</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>1315; 7750</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>662; 6284</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>0; 3377</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2734; 11100</t>
+          <t>3191; 10112</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1954; 8664</t>
+          <t>1960; 8739</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>565; 4956</t>
+          <t>564; 5027</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 3777</t>
+          <t>0; 3306</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>15919</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>8349</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>6299</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>9262</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>19275</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>9636</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>9356</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>30742</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>15919</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>8349</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>6299</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>9741</t>
+          <t>6765</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>40484</t>
+          <t>16027</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>13083; 27980</t>
+          <t>9852; 23333</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5181; 16126</t>
+          <t>4124; 14750</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5374; 14832</t>
+          <t>2843; 11734</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2726; 120684</t>
+          <t>5004; 15530</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>10573; 23863</t>
+          <t>12995; 27039</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4120; 14360</t>
+          <t>5602; 15733</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3006; 11106</t>
+          <t>5554; 15242</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>5172; 17084</t>
+          <t>2520; 18098</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>26373; 45436</t>
+          <t>27146; 46590</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11791; 25853</t>
+          <t>11412; 26523</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10130; 22399</t>
+          <t>10316; 22588</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>11809; 171521</t>
+          <t>9797; 26514</t>
         </is>
       </c>
     </row>
